--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/115.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/115.xlsx
@@ -426,13 +426,13 @@
         <v>-15.02750284659058</v>
       </c>
       <c r="E2">
-        <v>-15.68605186613073</v>
+        <v>-14.57824221268632</v>
       </c>
       <c r="F2">
-        <v>0.798197286374637</v>
+        <v>1.354209084277304</v>
       </c>
       <c r="G2">
-        <v>-15.63652078303443</v>
+        <v>-14.0631422330651</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.94995757076868</v>
       </c>
       <c r="E3">
-        <v>-15.3737773555098</v>
+        <v>-14.94289758215397</v>
       </c>
       <c r="F3">
-        <v>1.079257375940093</v>
+        <v>1.888857286861773</v>
       </c>
       <c r="G3">
-        <v>-15.71300933880665</v>
+        <v>-15.18486227598765</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.80937908235349</v>
       </c>
       <c r="E4">
-        <v>-17.21165853152281</v>
+        <v>-14.7992136303646</v>
       </c>
       <c r="F4">
-        <v>1.11637983272915</v>
+        <v>1.43845570587682</v>
       </c>
       <c r="G4">
-        <v>-15.69428504797768</v>
+        <v>-14.66177321620253</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.60136885705784</v>
       </c>
       <c r="E5">
-        <v>-17.30866750171513</v>
+        <v>-16.78687861265532</v>
       </c>
       <c r="F5">
-        <v>1.07001279572485</v>
+        <v>1.578241048364431</v>
       </c>
       <c r="G5">
-        <v>-15.32865852960875</v>
+        <v>-13.96048265413475</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.34813626217705</v>
       </c>
       <c r="E6">
-        <v>-17.40865167933048</v>
+        <v>-17.28101663942429</v>
       </c>
       <c r="F6">
-        <v>1.208616886296069</v>
+        <v>2.26589533718519</v>
       </c>
       <c r="G6">
-        <v>-14.71102107058824</v>
+        <v>-13.70422745339602</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.07185272325982</v>
       </c>
       <c r="E7">
-        <v>-18.12215351550502</v>
+        <v>-17.74279871940846</v>
       </c>
       <c r="F7">
-        <v>1.196975010817125</v>
+        <v>2.302837209880437</v>
       </c>
       <c r="G7">
-        <v>-14.17541415055384</v>
+        <v>-13.05662259787309</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.7715305551133</v>
       </c>
       <c r="E8">
-        <v>-20.03001772883257</v>
+        <v>-18.94584218123418</v>
       </c>
       <c r="F8">
-        <v>1.629790351840644</v>
+        <v>2.171804397370805</v>
       </c>
       <c r="G8">
-        <v>-13.84239313082112</v>
+        <v>-12.89234167805637</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.4688815207903</v>
       </c>
       <c r="E9">
-        <v>-19.64751564330068</v>
+        <v>-19.57902700240868</v>
       </c>
       <c r="F9">
-        <v>1.72692637022772</v>
+        <v>2.610472982462506</v>
       </c>
       <c r="G9">
-        <v>-13.14711212603946</v>
+        <v>-12.15451963575651</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.15056454125361</v>
       </c>
       <c r="E10">
-        <v>-20.97690352994041</v>
+        <v>-22.06926203007065</v>
       </c>
       <c r="F10">
-        <v>1.901713548953221</v>
+        <v>2.289631376745007</v>
       </c>
       <c r="G10">
-        <v>-12.07933044372184</v>
+        <v>-13.87577463835613</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.82262156741214</v>
       </c>
       <c r="E11">
-        <v>-21.44970338718524</v>
+        <v>-20.3221043023273</v>
       </c>
       <c r="F11">
-        <v>1.98963646508636</v>
+        <v>2.939649620986974</v>
       </c>
       <c r="G11">
-        <v>-11.68845820667455</v>
+        <v>-11.28159657696808</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.48194861285119</v>
       </c>
       <c r="E12">
-        <v>-22.31873566315321</v>
+        <v>-21.84131676242056</v>
       </c>
       <c r="F12">
-        <v>2.261833023441861</v>
+        <v>2.857879817921829</v>
       </c>
       <c r="G12">
-        <v>-10.5631534291983</v>
+        <v>-11.59866429747878</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.11925004502332</v>
       </c>
       <c r="E13">
-        <v>-23.67331997917162</v>
+        <v>-22.92820486594954</v>
       </c>
       <c r="F13">
-        <v>2.494924013446003</v>
+        <v>2.761104967722373</v>
       </c>
       <c r="G13">
-        <v>-10.64138103239702</v>
+        <v>-10.28274351594972</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.75335339478492</v>
       </c>
       <c r="E14">
-        <v>-25.12645747501895</v>
+        <v>-23.02174049657797</v>
       </c>
       <c r="F14">
-        <v>2.737107164063272</v>
+        <v>2.971775365602344</v>
       </c>
       <c r="G14">
-        <v>-9.771033732532754</v>
+        <v>-10.25176222198544</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.37760136818975</v>
       </c>
       <c r="E15">
-        <v>-25.68817391940439</v>
+        <v>-24.20929657729745</v>
       </c>
       <c r="F15">
-        <v>3.083648040085223</v>
+        <v>3.581006455665268</v>
       </c>
       <c r="G15">
-        <v>-10.44879301418698</v>
+        <v>-9.81266259045743</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.01362418118594</v>
       </c>
       <c r="E16">
-        <v>-27.06012946171622</v>
+        <v>-25.52184759757666</v>
       </c>
       <c r="F16">
-        <v>3.323973990985415</v>
+        <v>3.98308770931012</v>
       </c>
       <c r="G16">
-        <v>-9.394700588215361</v>
+        <v>-9.417610077143404</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.66257916052008</v>
       </c>
       <c r="E17">
-        <v>-27.23119256735596</v>
+        <v>-27.3511790146632</v>
       </c>
       <c r="F17">
-        <v>3.393306685864928</v>
+        <v>3.334583720680471</v>
       </c>
       <c r="G17">
-        <v>-8.806256157409225</v>
+        <v>-8.793826890142048</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.33081023030781</v>
       </c>
       <c r="E18">
-        <v>-28.68830153490802</v>
+        <v>-27.65644344752025</v>
       </c>
       <c r="F18">
-        <v>3.505005403193219</v>
+        <v>3.934475796644234</v>
       </c>
       <c r="G18">
-        <v>-8.651366093695637</v>
+        <v>-9.069164034859732</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.02710380655373</v>
       </c>
       <c r="E19">
-        <v>-28.9785223771116</v>
+        <v>-29.07238858634259</v>
       </c>
       <c r="F19">
-        <v>3.565166414188936</v>
+        <v>4.293425616360121</v>
       </c>
       <c r="G19">
-        <v>-8.212230368730472</v>
+        <v>-7.682066995263193</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.738211915146509</v>
       </c>
       <c r="E20">
-        <v>-30.44191913082331</v>
+        <v>-29.28670767570361</v>
       </c>
       <c r="F20">
-        <v>3.918413752703952</v>
+        <v>4.748207604171078</v>
       </c>
       <c r="G20">
-        <v>-8.866837351061253</v>
+        <v>-7.316433914451149</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.470965440018448</v>
       </c>
       <c r="E21">
-        <v>-30.36608077661685</v>
+        <v>-30.53504493455405</v>
       </c>
       <c r="F21">
-        <v>4.119615911169924</v>
+        <v>4.461281016658996</v>
       </c>
       <c r="G21">
-        <v>-8.407935547421992</v>
+        <v>-7.706574439090685</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.207300132214806</v>
       </c>
       <c r="E22">
-        <v>-31.09961205332732</v>
+        <v>-29.98992761164373</v>
       </c>
       <c r="F22">
-        <v>3.922220929287218</v>
+        <v>4.759586058815932</v>
       </c>
       <c r="G22">
-        <v>-7.885712730128569</v>
+        <v>-7.770640290038843</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.943858264018235</v>
       </c>
       <c r="E23">
-        <v>-30.87578996126121</v>
+        <v>-32.07575632499871</v>
       </c>
       <c r="F23">
-        <v>4.080253548923697</v>
+        <v>4.945471704004141</v>
       </c>
       <c r="G23">
-        <v>-8.7769778174343</v>
+        <v>-7.566656589352843</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.674238693679989</v>
       </c>
       <c r="E24">
-        <v>-31.42194204048228</v>
+        <v>-31.52186508369853</v>
       </c>
       <c r="F24">
-        <v>4.07034793152102</v>
+        <v>4.478419938222919</v>
       </c>
       <c r="G24">
-        <v>-8.413667841486342</v>
+        <v>-8.187086367920447</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.38559712203562</v>
       </c>
       <c r="E25">
-        <v>-31.1643080972379</v>
+        <v>-31.7033323583709</v>
       </c>
       <c r="F25">
-        <v>4.020584588165243</v>
+        <v>4.928172079164076</v>
       </c>
       <c r="G25">
-        <v>-7.97623178928897</v>
+        <v>-7.911342351729392</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.086268731000418</v>
       </c>
       <c r="E26">
-        <v>-31.47799549174922</v>
+        <v>-31.21659159389345</v>
       </c>
       <c r="F26">
-        <v>3.720057864633999</v>
+        <v>5.12048585539801</v>
       </c>
       <c r="G26">
-        <v>-7.754194807582906</v>
+        <v>-8.074652029964515</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.765639809653163</v>
       </c>
       <c r="E27">
-        <v>-32.22383742504954</v>
+        <v>-29.65229591081684</v>
       </c>
       <c r="F27">
-        <v>3.968506786286043</v>
+        <v>5.177157782893135</v>
       </c>
       <c r="G27">
-        <v>-8.07231580021419</v>
+        <v>-6.34892964421172</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.434609255242067</v>
       </c>
       <c r="E28">
-        <v>-30.35435429317399</v>
+        <v>-31.09141325113643</v>
       </c>
       <c r="F28">
-        <v>3.683462249513122</v>
+        <v>4.946190726909771</v>
       </c>
       <c r="G28">
-        <v>-8.060359028851574</v>
+        <v>-6.933912386272644</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.095299076551123</v>
       </c>
       <c r="E29">
-        <v>-30.7897670690115</v>
+        <v>-30.56764994740928</v>
       </c>
       <c r="F29">
-        <v>3.877232295641177</v>
+        <v>4.413782429782473</v>
       </c>
       <c r="G29">
-        <v>-8.176327242427028</v>
+        <v>-6.759216869226247</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.757771603717435</v>
       </c>
       <c r="E30">
-        <v>-30.71127050056254</v>
+        <v>-29.17121347461198</v>
       </c>
       <c r="F30">
-        <v>3.889715792401366</v>
+        <v>4.517581835557667</v>
       </c>
       <c r="G30">
-        <v>-7.605548908496941</v>
+        <v>-6.600120279473451</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.440944619332257</v>
       </c>
       <c r="E31">
-        <v>-29.6939533432134</v>
+        <v>-30.03711883927766</v>
       </c>
       <c r="F31">
-        <v>3.397914065359299</v>
+        <v>4.613024670973421</v>
       </c>
       <c r="G31">
-        <v>-7.737526202060927</v>
+        <v>-6.475286205244377</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.151112591642503</v>
       </c>
       <c r="E32">
-        <v>-28.82086808300856</v>
+        <v>-28.97577359338894</v>
       </c>
       <c r="F32">
-        <v>3.58964135747205</v>
+        <v>4.451935375620613</v>
       </c>
       <c r="G32">
-        <v>-7.752688726887121</v>
+        <v>-6.895164440877161</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.911273525690638</v>
       </c>
       <c r="E33">
-        <v>-28.44681612997499</v>
+        <v>-27.46243909255765</v>
       </c>
       <c r="F33">
-        <v>3.577863629739047</v>
+        <v>4.788575604444303</v>
       </c>
       <c r="G33">
-        <v>-8.311195292184884</v>
+        <v>-7.654649107912472</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.724239114401553</v>
       </c>
       <c r="E34">
-        <v>-28.47889131137132</v>
+        <v>-28.1077647525467</v>
       </c>
       <c r="F34">
-        <v>3.558339010055063</v>
+        <v>4.614615136386796</v>
       </c>
       <c r="G34">
-        <v>-8.154192121787014</v>
+        <v>-7.660972021857522</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.600497236164867</v>
       </c>
       <c r="E35">
-        <v>-27.88339697936267</v>
+        <v>-25.49135285360901</v>
       </c>
       <c r="F35">
-        <v>3.583594275431614</v>
+        <v>4.873824550601206</v>
       </c>
       <c r="G35">
-        <v>-8.142862063742252</v>
+        <v>-7.014397469904263</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.540113081779016</v>
       </c>
       <c r="E36">
-        <v>-27.09448699401241</v>
+        <v>-28.02845758725038</v>
       </c>
       <c r="F36">
-        <v>3.92568350503092</v>
+        <v>4.772177243338485</v>
       </c>
       <c r="G36">
-        <v>-8.475246526492441</v>
+        <v>-8.221158572593721</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.532176286761492</v>
       </c>
       <c r="E37">
-        <v>-26.2953969990929</v>
+        <v>-26.79655868904777</v>
       </c>
       <c r="F37">
-        <v>4.216959021407699</v>
+        <v>4.867729423251408</v>
       </c>
       <c r="G37">
-        <v>-8.591884109266022</v>
+        <v>-7.161071354833001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.575656295200426</v>
       </c>
       <c r="E38">
-        <v>-25.74228918379605</v>
+        <v>-24.85763367250161</v>
       </c>
       <c r="F38">
-        <v>4.16392859701528</v>
+        <v>5.156705391718015</v>
       </c>
       <c r="G38">
-        <v>-8.975025788319263</v>
+        <v>-7.604003453142443</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.651103731336835</v>
       </c>
       <c r="E39">
-        <v>-25.1166261579483</v>
+        <v>-24.68868536422345</v>
       </c>
       <c r="F39">
-        <v>4.254343242296041</v>
+        <v>4.94491504110946</v>
       </c>
       <c r="G39">
-        <v>-8.862729261668827</v>
+        <v>-8.407997890631622</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.754903825400897</v>
       </c>
       <c r="E40">
-        <v>-25.29255284467228</v>
+        <v>-23.78714770182842</v>
       </c>
       <c r="F40">
-        <v>4.381749462316216</v>
+        <v>5.379105472021626</v>
       </c>
       <c r="G40">
-        <v>-9.85165662746987</v>
+        <v>-7.828055104886007</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.872477888187065</v>
       </c>
       <c r="E41">
-        <v>-24.23389524810712</v>
+        <v>-24.33580402717573</v>
       </c>
       <c r="F41">
-        <v>4.427480313155166</v>
+        <v>4.989178024910649</v>
       </c>
       <c r="G41">
-        <v>-9.498518438356193</v>
+        <v>-8.973631269156499</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.997092867690052</v>
       </c>
       <c r="E42">
-        <v>-24.5447206470456</v>
+        <v>-22.34111085322511</v>
       </c>
       <c r="F42">
-        <v>4.188232896613417</v>
+        <v>4.80015286726583</v>
       </c>
       <c r="G42">
-        <v>-9.840694066239767</v>
+        <v>-8.914510219098425</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.126614778288281</v>
       </c>
       <c r="E43">
-        <v>-22.54560315398948</v>
+        <v>-22.24157952301053</v>
       </c>
       <c r="F43">
-        <v>4.425144317079271</v>
+        <v>4.97723296696228</v>
       </c>
       <c r="G43">
-        <v>-10.13163013825105</v>
+        <v>-7.991876653684403</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.250837034611396</v>
       </c>
       <c r="E44">
-        <v>-22.02599698940137</v>
+        <v>-21.81073597744676</v>
       </c>
       <c r="F44">
-        <v>4.338084559779849</v>
+        <v>5.620766751175132</v>
       </c>
       <c r="G44">
-        <v>-10.41090146761851</v>
+        <v>-9.302120921915629</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.374762175351469</v>
       </c>
       <c r="E45">
-        <v>-21.83437008329279</v>
+        <v>-23.28463199814525</v>
       </c>
       <c r="F45">
-        <v>4.589860204921536</v>
+        <v>4.644709724130502</v>
       </c>
       <c r="G45">
-        <v>-10.73806550686762</v>
+        <v>-9.348297552921695</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.489327096698088</v>
       </c>
       <c r="E46">
-        <v>-21.2381466669689</v>
+        <v>-21.50479227348855</v>
       </c>
       <c r="F46">
-        <v>4.245405158019834</v>
+        <v>5.44492920258288</v>
       </c>
       <c r="G46">
-        <v>-10.98650319724098</v>
+        <v>-9.647423553945353</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.599998827974676</v>
       </c>
       <c r="E47">
-        <v>-20.121194024503</v>
+        <v>-20.67470940246055</v>
       </c>
       <c r="F47">
-        <v>4.362110527930645</v>
+        <v>5.00890310950611</v>
       </c>
       <c r="G47">
-        <v>-10.02776635100839</v>
+        <v>-9.169310198075545</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.706911557234701</v>
       </c>
       <c r="E48">
-        <v>-20.34394966094031</v>
+        <v>-20.05039133339308</v>
       </c>
       <c r="F48">
-        <v>4.525688238961464</v>
+        <v>4.895877347598534</v>
       </c>
       <c r="G48">
-        <v>-10.96944412635343</v>
+        <v>-9.554299204866753</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.808356117442398</v>
       </c>
       <c r="E49">
-        <v>-19.7347295242144</v>
+        <v>-19.52190030280191</v>
       </c>
       <c r="F49">
-        <v>4.564349802384922</v>
+        <v>5.273609569805498</v>
       </c>
       <c r="G49">
-        <v>-10.97664312645485</v>
+        <v>-9.66588042521723</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.913324072311789</v>
       </c>
       <c r="E50">
-        <v>-18.00345768328997</v>
+        <v>-19.28923636523583</v>
       </c>
       <c r="F50">
-        <v>4.530749563792568</v>
+        <v>5.302826088102236</v>
       </c>
       <c r="G50">
-        <v>-11.0843426617005</v>
+        <v>-10.48836454619388</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.016255924363294</v>
       </c>
       <c r="E51">
-        <v>-18.50194304510631</v>
+        <v>-17.4054772190511</v>
       </c>
       <c r="F51">
-        <v>4.905724979283015</v>
+        <v>5.237257494701044</v>
       </c>
       <c r="G51">
-        <v>-11.54874379267339</v>
+        <v>-9.980329730923495</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.126831014641477</v>
       </c>
       <c r="E52">
-        <v>-18.24496573059303</v>
+        <v>-16.9737868488479</v>
       </c>
       <c r="F52">
-        <v>4.700604643001801</v>
+        <v>5.448956724895292</v>
       </c>
       <c r="G52">
-        <v>-11.59887101443703</v>
+        <v>-10.04640697068759</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.240779244837837</v>
       </c>
       <c r="E53">
-        <v>-17.00785908728162</v>
+        <v>-17.15706777736035</v>
       </c>
       <c r="F53">
-        <v>4.699264344544072</v>
+        <v>5.004255968376405</v>
       </c>
       <c r="G53">
-        <v>-11.48850056484199</v>
+        <v>-11.27495538453176</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.357616027481809</v>
       </c>
       <c r="E54">
-        <v>-16.7906463030297</v>
+        <v>-16.10995326104074</v>
       </c>
       <c r="F54">
-        <v>4.759291160020536</v>
+        <v>5.008513776826795</v>
       </c>
       <c r="G54">
-        <v>-12.10750301203123</v>
+        <v>-10.05348128436976</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.476333353406959</v>
       </c>
       <c r="E55">
-        <v>-16.63422375385675</v>
+        <v>-15.56914025267471</v>
       </c>
       <c r="F55">
-        <v>4.645509927041607</v>
+        <v>5.081625483797879</v>
       </c>
       <c r="G55">
-        <v>-12.34096192598572</v>
+        <v>-11.26380251245121</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.583572353636326</v>
       </c>
       <c r="E56">
-        <v>-15.3000402132429</v>
+        <v>-16.49820198008836</v>
       </c>
       <c r="F56">
-        <v>4.934972975541061</v>
+        <v>5.133204608500593</v>
       </c>
       <c r="G56">
-        <v>-12.37609724644426</v>
+        <v>-10.77627533192736</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.684907724600634</v>
       </c>
       <c r="E57">
-        <v>-15.28237463613898</v>
+        <v>-15.77217438480861</v>
       </c>
       <c r="F57">
-        <v>5.051620359733676</v>
+        <v>5.43617335913529</v>
       </c>
       <c r="G57">
-        <v>-12.65301265873203</v>
+        <v>-11.43900661883932</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.775388316469427</v>
       </c>
       <c r="E58">
-        <v>-14.22918743617508</v>
+        <v>-15.39970739767772</v>
       </c>
       <c r="F58">
-        <v>5.196346085411583</v>
+        <v>4.636397885610812</v>
       </c>
       <c r="G58">
-        <v>-12.7369003691208</v>
+        <v>-12.41057960381246</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.865867565523732</v>
       </c>
       <c r="E59">
-        <v>-14.10794660156773</v>
+        <v>-15.45940174204683</v>
       </c>
       <c r="F59">
-        <v>4.965733570676617</v>
+        <v>5.658744083123878</v>
       </c>
       <c r="G59">
-        <v>-12.32555330954257</v>
+        <v>-11.37996759932023</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.957307961968795</v>
       </c>
       <c r="E60">
-        <v>-13.92852846138383</v>
+        <v>-14.11722544480944</v>
       </c>
       <c r="F60">
-        <v>5.060588265236383</v>
+        <v>4.866172092534145</v>
       </c>
       <c r="G60">
-        <v>-12.44709631854752</v>
+        <v>-11.29960720210787</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.040414942882425</v>
       </c>
       <c r="E61">
-        <v>-13.49397156713377</v>
+        <v>-13.39433608201701</v>
       </c>
       <c r="F61">
-        <v>4.979489439767506</v>
+        <v>5.011326912526702</v>
       </c>
       <c r="G61">
-        <v>-13.18236885169569</v>
+        <v>-11.00839878870715</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.115255135242933</v>
       </c>
       <c r="E62">
-        <v>-13.42253488966277</v>
+        <v>-13.67755137493072</v>
       </c>
       <c r="F62">
-        <v>4.802579983756032</v>
+        <v>5.360213725033381</v>
       </c>
       <c r="G62">
-        <v>-12.62464321712907</v>
+        <v>-12.25251988007245</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.166067913069625</v>
       </c>
       <c r="E63">
-        <v>-12.11889137775665</v>
+        <v>-10.92588301433193</v>
       </c>
       <c r="F63">
-        <v>4.905627231929484</v>
+        <v>5.059133652077067</v>
       </c>
       <c r="G63">
-        <v>-13.07864943820164</v>
+        <v>-11.89125738637759</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.195444795138652</v>
       </c>
       <c r="E64">
-        <v>-12.36909862362845</v>
+        <v>-12.46938620900232</v>
       </c>
       <c r="F64">
-        <v>4.904250485306032</v>
+        <v>5.237572274314108</v>
       </c>
       <c r="G64">
-        <v>-13.03658417780956</v>
+        <v>-12.39614879139402</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.197148570038165</v>
       </c>
       <c r="E65">
-        <v>-13.0524408229119</v>
+        <v>-12.06258433194528</v>
       </c>
       <c r="F65">
-        <v>4.916356246530544</v>
+        <v>4.739713524822772</v>
       </c>
       <c r="G65">
-        <v>-12.5618898548047</v>
+        <v>-12.03876470158242</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.16970216594998</v>
       </c>
       <c r="E66">
-        <v>-12.09960913543199</v>
+        <v>-13.76637739259117</v>
       </c>
       <c r="F66">
-        <v>4.85567833427548</v>
+        <v>5.323556810724697</v>
       </c>
       <c r="G66">
-        <v>-13.04739580284793</v>
+        <v>-13.09906191752295</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.118860863358528</v>
       </c>
       <c r="E67">
-        <v>-11.89354998266097</v>
+        <v>-11.23249693244327</v>
       </c>
       <c r="F67">
-        <v>4.959651697205263</v>
+        <v>4.890898859507709</v>
       </c>
       <c r="G67">
-        <v>-12.77678689839741</v>
+        <v>-11.14994412433848</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.037778757030319</v>
       </c>
       <c r="E68">
-        <v>-12.27436294738799</v>
+        <v>-12.29848159995284</v>
       </c>
       <c r="F68">
-        <v>4.57481208268228</v>
+        <v>4.719622301835273</v>
       </c>
       <c r="G68">
-        <v>-12.94570746549918</v>
+        <v>-11.14226606588938</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.935788138329262</v>
       </c>
       <c r="E69">
-        <v>-12.09581427421356</v>
+        <v>-12.08371419166507</v>
       </c>
       <c r="F69">
-        <v>4.407790019990621</v>
+        <v>4.865307276965622</v>
       </c>
       <c r="G69">
-        <v>-12.58460247043917</v>
+        <v>-11.97823600747535</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.807651554051382</v>
       </c>
       <c r="E70">
-        <v>-11.72699723713286</v>
+        <v>-12.44606456786282</v>
       </c>
       <c r="F70">
-        <v>4.076631926638657</v>
+        <v>4.744730117814126</v>
       </c>
       <c r="G70">
-        <v>-12.80190793065652</v>
+        <v>-11.65497990310353</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.657922779559239</v>
       </c>
       <c r="E71">
-        <v>-10.9445222133475</v>
+        <v>-11.36992706162805</v>
       </c>
       <c r="F71">
-        <v>4.170058515795997</v>
+        <v>3.975513117778922</v>
       </c>
       <c r="G71">
-        <v>-12.7110180934599</v>
+        <v>-13.07524024900138</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.489473657498227</v>
       </c>
       <c r="E72">
-        <v>-11.47855609612405</v>
+        <v>-12.99231174503806</v>
       </c>
       <c r="F72">
-        <v>4.278506719435702</v>
+        <v>4.150654837752821</v>
       </c>
       <c r="G72">
-        <v>-12.32466409849996</v>
+        <v>-11.75202203072411</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.297839376458721</v>
       </c>
       <c r="E73">
-        <v>-11.26000741203987</v>
+        <v>-12.11928988346933</v>
       </c>
       <c r="F73">
-        <v>3.577779136263961</v>
+        <v>3.65859134661147</v>
       </c>
       <c r="G73">
-        <v>-12.73267087453067</v>
+        <v>-12.38714511943491</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.093013789139096</v>
       </c>
       <c r="E74">
-        <v>-11.84842373917453</v>
+        <v>-12.04062123300808</v>
       </c>
       <c r="F74">
-        <v>3.98763544635149</v>
+        <v>4.010089173171773</v>
       </c>
       <c r="G74">
-        <v>-12.38754870968672</v>
+        <v>-10.86235489831783</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.86967423647093</v>
       </c>
       <c r="E75">
-        <v>-12.20344704442787</v>
+        <v>-11.89207370013447</v>
       </c>
       <c r="F75">
-        <v>3.744986753253847</v>
+        <v>3.648940866368856</v>
       </c>
       <c r="G75">
-        <v>-12.295825442214</v>
+        <v>-11.13147412818037</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.635326512222842</v>
       </c>
       <c r="E76">
-        <v>-12.81632165967796</v>
+        <v>-12.27169567619747</v>
       </c>
       <c r="F76">
-        <v>3.698293339492845</v>
+        <v>3.80433596419482</v>
       </c>
       <c r="G76">
-        <v>-12.29812229730561</v>
+        <v>-11.88656523954758</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.391341907429965</v>
       </c>
       <c r="E77">
-        <v>-12.96871386698409</v>
+        <v>-12.76458384414033</v>
       </c>
       <c r="F77">
-        <v>3.578821222456683</v>
+        <v>3.25312869722839</v>
       </c>
       <c r="G77">
-        <v>-11.73733528302404</v>
+        <v>-10.86875984280186</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.138057663362942</v>
       </c>
       <c r="E78">
-        <v>-13.28803921163496</v>
+        <v>-12.45879410829838</v>
       </c>
       <c r="F78">
-        <v>3.508330469948056</v>
+        <v>3.503030575304945</v>
       </c>
       <c r="G78">
-        <v>-11.08048722636815</v>
+        <v>-10.18926807616426</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.885813786071618</v>
       </c>
       <c r="E79">
-        <v>-14.03235278495768</v>
+        <v>-13.5397453824033</v>
       </c>
       <c r="F79">
-        <v>3.528767950509926</v>
+        <v>3.825384779899956</v>
       </c>
       <c r="G79">
-        <v>-10.72158721219609</v>
+        <v>-10.17675021591497</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.631501765690916</v>
       </c>
       <c r="E80">
-        <v>-13.76187608942755</v>
+        <v>-13.59053674687333</v>
       </c>
       <c r="F80">
-        <v>3.429234636859148</v>
+        <v>3.803997990294478</v>
       </c>
       <c r="G80">
-        <v>-10.77796187980891</v>
+        <v>-9.994320859652968</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.385297923527779</v>
       </c>
       <c r="E81">
-        <v>-13.84174478550083</v>
+        <v>-14.60216161239483</v>
       </c>
       <c r="F81">
-        <v>3.459329224602854</v>
+        <v>3.479274654927461</v>
       </c>
       <c r="G81">
-        <v>-9.919121823953613</v>
+        <v>-8.008633852188487</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.145810342534233</v>
       </c>
       <c r="E82">
-        <v>-15.8169836351145</v>
+        <v>-15.0196054033699</v>
       </c>
       <c r="F82">
-        <v>3.04515380687713</v>
+        <v>3.250950090959027</v>
       </c>
       <c r="G82">
-        <v>-10.06922130419041</v>
+        <v>-9.454881472837137</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.916552978123851</v>
       </c>
       <c r="E83">
-        <v>-15.67453142825522</v>
+        <v>-15.03704908524745</v>
       </c>
       <c r="F83">
-        <v>2.962964849906168</v>
+        <v>2.89540320453384</v>
       </c>
       <c r="G83">
-        <v>-9.581431625941802</v>
+        <v>-9.73702715229067</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.701558009759029</v>
       </c>
       <c r="E84">
-        <v>-16.26675167355632</v>
+        <v>-17.1199659898155</v>
       </c>
       <c r="F84">
-        <v>3.139874305917642</v>
+        <v>3.200456127553981</v>
       </c>
       <c r="G84">
-        <v>-9.402188335814014</v>
+        <v>-9.378202606214474</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.495590474248973</v>
       </c>
       <c r="E85">
-        <v>-17.39066910904602</v>
+        <v>-17.3995720889451</v>
       </c>
       <c r="F85">
-        <v>2.773439358350058</v>
+        <v>2.942694699559664</v>
       </c>
       <c r="G85">
-        <v>-8.692844015428577</v>
+        <v>-8.752303031307274</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.304215145066432</v>
       </c>
       <c r="E86">
-        <v>-18.13131008994852</v>
+        <v>-17.75660150818384</v>
       </c>
       <c r="F86">
-        <v>2.781524224201382</v>
+        <v>2.590812510524462</v>
       </c>
       <c r="G86">
-        <v>-8.656747297053126</v>
+        <v>-7.892216111259389</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.120494077362742</v>
       </c>
       <c r="E87">
-        <v>-19.74277662252604</v>
+        <v>-19.52141575608309</v>
       </c>
       <c r="F87">
-        <v>2.472715483376948</v>
+        <v>2.486090303462549</v>
       </c>
       <c r="G87">
-        <v>-8.244350246575877</v>
+        <v>-7.30679696673106</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.945539551781267</v>
       </c>
       <c r="E88">
-        <v>-20.99597746246071</v>
+        <v>-21.14779002509386</v>
       </c>
       <c r="F88">
-        <v>2.219765213258091</v>
+        <v>2.820583403978184</v>
       </c>
       <c r="G88">
-        <v>-8.13808788637326</v>
+        <v>-7.494863461632193</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.777137533289132</v>
       </c>
       <c r="E89">
-        <v>-21.7552666993268</v>
+        <v>-23.20823664163585</v>
       </c>
       <c r="F89">
-        <v>1.974266936294818</v>
+        <v>2.536628998707347</v>
       </c>
       <c r="G89">
-        <v>-7.867469138258056</v>
+        <v>-5.476521737208119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.610985495509144</v>
       </c>
       <c r="E90">
-        <v>-24.15720101231322</v>
+        <v>-25.10429512322541</v>
       </c>
       <c r="F90">
-        <v>1.8030549912798</v>
+        <v>1.924540041104764</v>
       </c>
       <c r="G90">
-        <v>-7.790143870988183</v>
+        <v>-5.805972787884166</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.451477988500573</v>
       </c>
       <c r="E91">
-        <v>-25.18107540002546</v>
+        <v>-25.67795768204308</v>
       </c>
       <c r="F91">
-        <v>1.323695342627782</v>
+        <v>2.135066303056647</v>
       </c>
       <c r="G91">
-        <v>-7.102783735051025</v>
+        <v>-6.7899816025676</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.293628500026798</v>
       </c>
       <c r="E92">
-        <v>-27.75578005335251</v>
+        <v>-28.39885959023376</v>
       </c>
       <c r="F92">
-        <v>0.8167991047719028</v>
+        <v>1.485916187852815</v>
       </c>
       <c r="G92">
-        <v>-6.756578767092454</v>
+        <v>-6.044294472189754</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.141770290833254</v>
       </c>
       <c r="E93">
-        <v>-28.85850875896032</v>
+        <v>-29.74592663939944</v>
       </c>
       <c r="F93">
-        <v>0.5756480999385218</v>
+        <v>1.481873754927153</v>
       </c>
       <c r="G93">
-        <v>-6.282635843824699</v>
+        <v>-6.882433301226515</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.994196744704494</v>
       </c>
       <c r="E94">
-        <v>-31.34452098461014</v>
+        <v>-30.94038185026961</v>
       </c>
       <c r="F94">
-        <v>0.5525797245053613</v>
+        <v>1.221136831221981</v>
       </c>
       <c r="G94">
-        <v>-7.402779259787937</v>
+        <v>-6.600635431258284</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.853184943279547</v>
       </c>
       <c r="E95">
-        <v>-33.36301581794508</v>
+        <v>-33.34716389468123</v>
       </c>
       <c r="F95">
-        <v>0.1817063843935778</v>
+        <v>0.3497108908249567</v>
       </c>
       <c r="G95">
-        <v>-7.377231668726099</v>
+        <v>-7.02038241802869</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.724463397557056</v>
       </c>
       <c r="E96">
-        <v>-34.66285767592176</v>
+        <v>-36.32002103971067</v>
       </c>
       <c r="F96">
-        <v>-0.1179878298978525</v>
+        <v>0.443468826943416</v>
       </c>
       <c r="G96">
-        <v>-7.189289860244226</v>
+        <v>-6.919934382429409</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.606316542611778</v>
       </c>
       <c r="E97">
-        <v>-38.31233450057027</v>
+        <v>-38.03814672059085</v>
       </c>
       <c r="F97">
-        <v>-0.752896652712756</v>
+        <v>-0.6175091127666076</v>
       </c>
       <c r="G97">
-        <v>-7.096670819285779</v>
+        <v>-6.412608311015864</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.508017487969969</v>
       </c>
       <c r="E98">
-        <v>-40.05466034654743</v>
+        <v>-41.14726564851109</v>
       </c>
       <c r="F98">
-        <v>-0.7410667378333763</v>
+        <v>-0.5345530875806539</v>
       </c>
       <c r="G98">
-        <v>-7.601650817284321</v>
+        <v>-7.299109064617281</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.424576889609711</v>
       </c>
       <c r="E99">
-        <v>-42.03430313713356</v>
+        <v>-41.5349166089897</v>
       </c>
       <c r="F99">
-        <v>-1.299797237552032</v>
+        <v>-0.7512092683132534</v>
       </c>
       <c r="G99">
-        <v>-7.83258319063804</v>
+        <v>-6.879834573751435</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.364779033839709</v>
       </c>
       <c r="E100">
-        <v>-45.10203634109771</v>
+        <v>-45.97326719119641</v>
       </c>
       <c r="F100">
-        <v>-1.712209889444599</v>
+        <v>-0.8399075363354133</v>
       </c>
       <c r="G100">
-        <v>-7.870031772295983</v>
+        <v>-7.203044741021418</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.318352174133601</v>
       </c>
       <c r="E101">
-        <v>-47.4404338995195</v>
+        <v>-47.16140744506288</v>
       </c>
       <c r="F101">
-        <v>-1.846390498084869</v>
+        <v>-1.477627009748016</v>
       </c>
       <c r="G101">
-        <v>-8.027779779987847</v>
+        <v>-7.164057266452096</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.298614117433036</v>
       </c>
       <c r="E102">
-        <v>-49.29290129031122</v>
+        <v>-49.73339727822233</v>
       </c>
       <c r="F102">
-        <v>-2.086922712468358</v>
+        <v>-1.377012676636585</v>
       </c>
       <c r="G102">
-        <v>-7.800591280433454</v>
+        <v>-7.508526468205721</v>
       </c>
     </row>
   </sheetData>
